--- a/01. Data/Persons.xlsx
+++ b/01. Data/Persons.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10208"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AndrewYongBusinessIn\Documents\01. Byner\DatabACE\01. Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andrewyong/Documents/GitHub/DatabACE/01. Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83C4BDD0-471A-434A-81C0-735EEEAF1B26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8606122E-7714-4C45-B0A4-68B5DB712413}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="19860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Person" sheetId="1" r:id="rId1"/>
@@ -51,6 +51,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>======
@@ -529,6 +530,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -536,17 +538,20 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color theme="10"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -569,13 +574,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -856,30 +860,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr codeName="Sheet1">
+  <sheetPr codeName="Sheet1" filterMode="1">
     <tabColor rgb="FFC00000"/>
   </sheetPr>
   <dimension ref="A1:P1000"/>
-  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.33203125" customWidth="1"/>
     <col min="2" max="2" width="15.6640625" customWidth="1"/>
     <col min="3" max="3" width="14.33203125" customWidth="1"/>
-    <col min="4" max="4" width="24.44140625" customWidth="1"/>
+    <col min="4" max="4" width="24.5" customWidth="1"/>
     <col min="5" max="5" width="10.33203125" customWidth="1"/>
-    <col min="6" max="6" width="28.44140625" customWidth="1"/>
-    <col min="7" max="7" width="12.88671875" customWidth="1"/>
-    <col min="8" max="8" width="11.44140625" customWidth="1"/>
-    <col min="9" max="9" width="8.88671875" customWidth="1"/>
+    <col min="6" max="6" width="28.5" customWidth="1"/>
+    <col min="7" max="7" width="12.83203125" customWidth="1"/>
+    <col min="8" max="8" width="11.5" customWidth="1"/>
+    <col min="9" max="9" width="8.83203125" customWidth="1"/>
     <col min="10" max="10" width="9" customWidth="1"/>
-    <col min="11" max="11" width="13.44140625" customWidth="1"/>
-    <col min="12" max="12" width="16.109375" customWidth="1"/>
-    <col min="13" max="14" width="8.88671875" customWidth="1"/>
+    <col min="11" max="11" width="13.5" customWidth="1"/>
+    <col min="12" max="12" width="16.1640625" customWidth="1"/>
+    <col min="13" max="14" width="8.83203125" customWidth="1"/>
     <col min="15" max="15" width="12.33203125" customWidth="1"/>
-    <col min="16" max="26" width="8.88671875" customWidth="1"/>
+    <col min="16" max="26" width="8.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -929,7 +933,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -961,7 +965,7 @@
         <v>1</v>
       </c>
       <c r="M2" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N2" s="2" t="s">
         <v>18</v>
@@ -969,11 +973,11 @@
       <c r="O2" s="2">
         <v>5</v>
       </c>
-      <c r="P2" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="P2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -988,7 +992,7 @@
       </c>
       <c r="G3" s="3">
         <f t="shared" ref="G3:G29" ca="1" si="0">G2+3*RANDBETWEEN(-365, 365)</f>
-        <v>38624</v>
+        <v>38216</v>
       </c>
       <c r="H3" s="2">
         <v>1</v>
@@ -1006,7 +1010,7 @@
         <v>1</v>
       </c>
       <c r="M3" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N3" s="2" t="s">
         <v>18</v>
@@ -1014,11 +1018,11 @@
       <c r="O3" s="2">
         <v>5</v>
       </c>
-      <c r="P3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="P3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -1033,7 +1037,7 @@
       </c>
       <c r="G4" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>37568</v>
+        <v>37760</v>
       </c>
       <c r="H4" s="2">
         <v>1</v>
@@ -1059,11 +1063,11 @@
       <c r="O4" s="2">
         <v>5</v>
       </c>
-      <c r="P4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="P4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -1078,7 +1082,7 @@
       </c>
       <c r="G5" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>36518</v>
+        <v>38345</v>
       </c>
       <c r="H5" s="2">
         <v>2</v>
@@ -1104,11 +1108,11 @@
       <c r="O5" s="2">
         <v>0</v>
       </c>
-      <c r="P5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="P5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -1123,7 +1127,7 @@
       </c>
       <c r="G6" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>35690</v>
+        <v>38948</v>
       </c>
       <c r="H6" s="2">
         <v>3</v>
@@ -1149,11 +1153,11 @@
       <c r="O6" s="2">
         <v>0</v>
       </c>
-      <c r="P6" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="P6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -1171,7 +1175,7 @@
       </c>
       <c r="G7" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>35351</v>
+        <v>39419</v>
       </c>
       <c r="H7" s="2">
         <v>4</v>
@@ -1189,7 +1193,7 @@
         <v>2</v>
       </c>
       <c r="M7" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>18</v>
@@ -1197,11 +1201,11 @@
       <c r="O7" s="2">
         <v>0</v>
       </c>
-      <c r="P7" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="P7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -1219,7 +1223,7 @@
       </c>
       <c r="G8" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>35939</v>
+        <v>39590</v>
       </c>
       <c r="H8" s="2">
         <v>4</v>
@@ -1237,7 +1241,7 @@
         <v>2</v>
       </c>
       <c r="M8" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>18</v>
@@ -1245,11 +1249,11 @@
       <c r="O8" s="2">
         <v>0</v>
       </c>
-      <c r="P8" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="P8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -1267,7 +1271,7 @@
       </c>
       <c r="G9" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>35120</v>
+        <v>39428</v>
       </c>
       <c r="H9" s="2">
         <v>5</v>
@@ -1285,7 +1289,7 @@
         <v>2</v>
       </c>
       <c r="M9" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>18</v>
@@ -1293,11 +1297,11 @@
       <c r="O9" s="2">
         <v>0</v>
       </c>
-      <c r="P9" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="P9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -1312,7 +1316,7 @@
       </c>
       <c r="G10" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>35678</v>
+        <v>40478</v>
       </c>
       <c r="H10" s="2">
         <v>6</v>
@@ -1338,11 +1342,11 @@
       <c r="O10" s="2">
         <v>6</v>
       </c>
-      <c r="P10" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="P10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -1357,7 +1361,7 @@
       </c>
       <c r="G11" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>35972</v>
+        <v>39518</v>
       </c>
       <c r="H11" s="2">
         <v>7</v>
@@ -1383,11 +1387,11 @@
       <c r="O11" s="2">
         <v>3</v>
       </c>
-      <c r="P11" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="P11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -1402,7 +1406,7 @@
       </c>
       <c r="G12" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>35099</v>
+        <v>39983</v>
       </c>
       <c r="H12" s="2">
         <v>8</v>
@@ -1428,11 +1432,11 @@
       <c r="O12" s="2">
         <v>4</v>
       </c>
-      <c r="P12" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="P12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -1447,7 +1451,7 @@
       </c>
       <c r="G13" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>34586</v>
+        <v>39755</v>
       </c>
       <c r="H13" s="2">
         <v>9</v>
@@ -1473,11 +1477,11 @@
       <c r="O13" s="2">
         <v>1</v>
       </c>
-      <c r="P13" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="P13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -1492,7 +1496,7 @@
       </c>
       <c r="G14" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>35663</v>
+        <v>39884</v>
       </c>
       <c r="H14" s="2">
         <v>9</v>
@@ -1518,11 +1522,11 @@
       <c r="O14" s="2">
         <v>1</v>
       </c>
-      <c r="P14" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="P14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -1540,7 +1544,7 @@
       </c>
       <c r="G15" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>35003</v>
+        <v>38906</v>
       </c>
       <c r="H15" s="2">
         <v>10</v>
@@ -1566,11 +1570,11 @@
       <c r="O15" s="2">
         <v>0</v>
       </c>
-      <c r="P15" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="P15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -1588,7 +1592,7 @@
       </c>
       <c r="G16" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>35783</v>
+        <v>39068</v>
       </c>
       <c r="H16" s="2">
         <v>10</v>
@@ -1614,11 +1618,11 @@
       <c r="O16" s="2">
         <v>0</v>
       </c>
-      <c r="P16" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="P16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -1636,7 +1640,7 @@
       </c>
       <c r="G17" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>35075</v>
+        <v>39539</v>
       </c>
       <c r="H17" s="2">
         <v>10</v>
@@ -1662,11 +1666,11 @@
       <c r="O17" s="2">
         <v>0</v>
       </c>
-      <c r="P17" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="P17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -1684,7 +1688,7 @@
       </c>
       <c r="G18" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>35444</v>
+        <v>40352</v>
       </c>
       <c r="H18" s="2">
         <v>11</v>
@@ -1710,11 +1714,11 @@
       <c r="O18" s="2">
         <v>0</v>
       </c>
-      <c r="P18" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="P18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -1732,7 +1736,7 @@
       </c>
       <c r="G19" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>34607</v>
+        <v>39806</v>
       </c>
       <c r="H19" s="2">
         <v>11</v>
@@ -1758,11 +1762,11 @@
       <c r="O19" s="2">
         <v>0</v>
       </c>
-      <c r="P19" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="P19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -1777,7 +1781,7 @@
       </c>
       <c r="G20" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>34196</v>
+        <v>39101</v>
       </c>
       <c r="H20" s="2">
         <v>12</v>
@@ -1795,7 +1799,7 @@
         <v>2</v>
       </c>
       <c r="M20" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N20" s="2" t="s">
         <v>18</v>
@@ -1803,11 +1807,11 @@
       <c r="O20" s="2">
         <v>0</v>
       </c>
-      <c r="P20" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -1822,7 +1826,7 @@
       </c>
       <c r="G21" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>33257</v>
+        <v>39674</v>
       </c>
       <c r="H21" s="2">
         <v>12</v>
@@ -1848,11 +1852,11 @@
       <c r="O21" s="2">
         <v>0</v>
       </c>
-      <c r="P21" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -1867,7 +1871,7 @@
       </c>
       <c r="G22" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>33017</v>
+        <v>39881</v>
       </c>
       <c r="H22" s="2">
         <v>13</v>
@@ -1893,11 +1897,11 @@
       <c r="O22" s="2">
         <v>4</v>
       </c>
-      <c r="P22" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -1912,7 +1916,7 @@
       </c>
       <c r="G23" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>33425</v>
+        <v>39698</v>
       </c>
       <c r="H23" s="2">
         <v>13</v>
@@ -1930,7 +1934,7 @@
         <v>2</v>
       </c>
       <c r="M23" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N23" s="2" t="s">
         <v>43</v>
@@ -1938,11 +1942,11 @@
       <c r="O23" s="2">
         <v>4</v>
       </c>
-      <c r="P23" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -1957,7 +1961,7 @@
       </c>
       <c r="G24" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>34076</v>
+        <v>39284</v>
       </c>
       <c r="H24" s="2">
         <v>13</v>
@@ -1983,11 +1987,11 @@
       <c r="O24" s="2">
         <v>4</v>
       </c>
-      <c r="P24" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -2002,7 +2006,7 @@
       </c>
       <c r="G25" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>33521</v>
+        <v>39032</v>
       </c>
       <c r="H25" s="2">
         <v>14</v>
@@ -2028,11 +2032,11 @@
       <c r="O25" s="2">
         <v>4</v>
       </c>
-      <c r="P25" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -2047,7 +2051,7 @@
       </c>
       <c r="G26" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>33482</v>
+        <v>38096</v>
       </c>
       <c r="H26" s="2">
         <v>14</v>
@@ -2073,11 +2077,11 @@
       <c r="O26" s="2">
         <v>4</v>
       </c>
-      <c r="P26" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -2092,7 +2096,7 @@
       </c>
       <c r="G27" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>33575</v>
+        <v>39119</v>
       </c>
       <c r="H27" s="2">
         <v>15</v>
@@ -2118,11 +2122,11 @@
       <c r="O27" s="2">
         <v>0</v>
       </c>
-      <c r="P27" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -2137,7 +2141,7 @@
       </c>
       <c r="G28" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>32831</v>
+        <v>39746</v>
       </c>
       <c r="H28" s="2">
         <v>15</v>
@@ -2163,11 +2167,11 @@
       <c r="O28" s="2">
         <v>0</v>
       </c>
-      <c r="P28" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -2182,7 +2186,7 @@
       </c>
       <c r="G29" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>33137</v>
+        <v>38891</v>
       </c>
       <c r="H29" s="2">
         <v>16</v>
@@ -2208,11 +2212,11 @@
       <c r="O29" s="2">
         <v>0</v>
       </c>
-      <c r="P29" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -2252,11 +2256,11 @@
       <c r="O30" s="2">
         <v>4</v>
       </c>
-      <c r="P30" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -2299,11 +2303,11 @@
       <c r="O31" s="2">
         <v>4</v>
       </c>
-      <c r="P31" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -2321,7 +2325,7 @@
       </c>
       <c r="G32" s="3">
         <f t="shared" ref="G32:G61" ca="1" si="1">G31+3*RANDBETWEEN(-365, 365)</f>
-        <v>31322</v>
+        <v>30746</v>
       </c>
       <c r="H32" s="2">
         <v>20</v>
@@ -2347,11 +2351,11 @@
       <c r="O32" s="2">
         <v>0</v>
       </c>
-      <c r="P32" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
         <v>32</v>
       </c>
@@ -2369,7 +2373,7 @@
       </c>
       <c r="G33" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>32192</v>
+        <v>30221</v>
       </c>
       <c r="H33" s="2">
         <v>16</v>
@@ -2395,11 +2399,11 @@
       <c r="O33" s="2">
         <v>0</v>
       </c>
-      <c r="P33" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
         <v>33</v>
       </c>
@@ -2417,7 +2421,7 @@
       </c>
       <c r="G34" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>32369</v>
+        <v>31202</v>
       </c>
       <c r="H34" s="2">
         <v>14</v>
@@ -2443,11 +2447,11 @@
       <c r="O34" s="2">
         <v>0</v>
       </c>
-      <c r="P34" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
         <v>34</v>
       </c>
@@ -2462,7 +2466,7 @@
       </c>
       <c r="G35" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>31298</v>
+        <v>31778</v>
       </c>
       <c r="H35" s="2">
         <v>20</v>
@@ -2488,11 +2492,11 @@
       <c r="O35" s="2">
         <v>0</v>
       </c>
-      <c r="P35" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
         <v>35</v>
       </c>
@@ -2510,7 +2514,7 @@
       </c>
       <c r="G36" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>31790</v>
+        <v>32477</v>
       </c>
       <c r="H36" s="2">
         <v>20</v>
@@ -2536,11 +2540,11 @@
       <c r="O36" s="2">
         <v>0</v>
       </c>
-      <c r="P36" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
         <v>36</v>
       </c>
@@ -2558,7 +2562,7 @@
       </c>
       <c r="G37" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>31967</v>
+        <v>32816</v>
       </c>
       <c r="H37" s="2">
         <v>21</v>
@@ -2584,11 +2588,11 @@
       <c r="O37" s="2">
         <v>0</v>
       </c>
-      <c r="P37" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
         <v>37</v>
       </c>
@@ -2606,7 +2610,7 @@
       </c>
       <c r="G38" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>31565</v>
+        <v>33776</v>
       </c>
       <c r="H38" s="2">
         <v>12</v>
@@ -2632,11 +2636,11 @@
       <c r="O38" s="2">
         <v>0</v>
       </c>
-      <c r="P38" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
         <v>38</v>
       </c>
@@ -2651,7 +2655,7 @@
       </c>
       <c r="G39" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>31535</v>
+        <v>34055</v>
       </c>
       <c r="H39" s="2">
         <v>18</v>
@@ -2677,11 +2681,11 @@
       <c r="O39" s="2">
         <v>0</v>
       </c>
-      <c r="P39" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
         <v>39</v>
       </c>
@@ -2696,7 +2700,7 @@
       </c>
       <c r="G40" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>30788</v>
+        <v>34790</v>
       </c>
       <c r="H40" s="2">
         <v>18</v>
@@ -2722,11 +2726,11 @@
       <c r="O40" s="2">
         <v>0</v>
       </c>
-      <c r="P40" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
         <v>40</v>
       </c>
@@ -2741,7 +2745,7 @@
       </c>
       <c r="G41" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>30686</v>
+        <v>33884</v>
       </c>
       <c r="H41" s="2">
         <v>18</v>
@@ -2767,11 +2771,11 @@
       <c r="O41" s="2">
         <v>0</v>
       </c>
-      <c r="P41" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
         <v>41</v>
       </c>
@@ -2792,7 +2796,7 @@
       </c>
       <c r="G42" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>31451</v>
+        <v>33188</v>
       </c>
       <c r="H42" s="2">
         <v>4</v>
@@ -2818,11 +2822,11 @@
       <c r="O42" s="2">
         <v>0</v>
       </c>
-      <c r="P42" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
         <v>42</v>
       </c>
@@ -2840,7 +2844,7 @@
       </c>
       <c r="G43" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>31133</v>
+        <v>34217</v>
       </c>
       <c r="H43" s="2">
         <v>9</v>
@@ -2866,11 +2870,11 @@
       <c r="O43" s="2">
         <v>0</v>
       </c>
-      <c r="P43" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
         <v>43</v>
       </c>
@@ -2885,7 +2889,7 @@
       </c>
       <c r="G44" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>31121</v>
+        <v>33791</v>
       </c>
       <c r="H44" s="2">
         <v>9</v>
@@ -2908,11 +2912,11 @@
       <c r="O44" s="2">
         <v>0</v>
       </c>
-      <c r="P44" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
         <v>44</v>
       </c>
@@ -2933,7 +2937,7 @@
       </c>
       <c r="G45" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>30668</v>
+        <v>34835</v>
       </c>
       <c r="H45" s="2">
         <v>10</v>
@@ -2959,11 +2963,11 @@
       <c r="O45" s="2">
         <v>0</v>
       </c>
-      <c r="P45" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
         <v>45</v>
       </c>
@@ -2981,7 +2985,7 @@
       </c>
       <c r="G46" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>31145</v>
+        <v>34490</v>
       </c>
       <c r="H46" s="2">
         <v>13</v>
@@ -3007,11 +3011,11 @@
       <c r="O46" s="2">
         <v>0</v>
       </c>
-      <c r="P46" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
         <v>46</v>
       </c>
@@ -3029,7 +3033,7 @@
       </c>
       <c r="G47" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>31520</v>
+        <v>35153</v>
       </c>
       <c r="H47" s="2">
         <v>13</v>
@@ -3055,11 +3059,11 @@
       <c r="O47" s="2">
         <v>0</v>
       </c>
-      <c r="P47" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
         <v>47</v>
       </c>
@@ -3077,7 +3081,7 @@
       </c>
       <c r="G48" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>31532</v>
+        <v>36128</v>
       </c>
       <c r="H48" s="2">
         <v>14</v>
@@ -3103,11 +3107,11 @@
       <c r="O48" s="2">
         <v>0</v>
       </c>
-      <c r="P48" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
         <v>48</v>
       </c>
@@ -3125,7 +3129,7 @@
       </c>
       <c r="G49" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>30647</v>
+        <v>37028</v>
       </c>
       <c r="H49" s="2">
         <v>18</v>
@@ -3151,11 +3155,11 @@
       <c r="O49" s="2">
         <v>0</v>
       </c>
-      <c r="P49" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
         <v>49</v>
       </c>
@@ -3176,7 +3180,7 @@
       </c>
       <c r="G50" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>31139</v>
+        <v>37613</v>
       </c>
       <c r="H50" s="2">
         <v>22</v>
@@ -3202,11 +3206,11 @@
       <c r="O50" s="2">
         <v>0</v>
       </c>
-      <c r="P50" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
         <v>50</v>
       </c>
@@ -3224,7 +3228,7 @@
       </c>
       <c r="G51" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>32003</v>
+        <v>38303</v>
       </c>
       <c r="H51" s="2">
         <v>23</v>
@@ -3250,11 +3254,11 @@
       <c r="O51" s="2">
         <v>0</v>
       </c>
-      <c r="P51" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
         <v>51</v>
       </c>
@@ -3272,7 +3276,7 @@
       </c>
       <c r="G52" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>32081</v>
+        <v>38906</v>
       </c>
       <c r="H52" s="2">
         <v>24</v>
@@ -3298,11 +3302,11 @@
       <c r="O52" s="2">
         <v>0</v>
       </c>
-      <c r="P52" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
         <v>52</v>
       </c>
@@ -3317,7 +3321,7 @@
       </c>
       <c r="G53" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>31394</v>
+        <v>39953</v>
       </c>
       <c r="H53" s="2">
         <v>25</v>
@@ -3340,11 +3344,11 @@
       <c r="O53" s="2">
         <v>0</v>
       </c>
-      <c r="P53" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
         <v>53</v>
       </c>
@@ -3359,7 +3363,7 @@
       </c>
       <c r="G54" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>30338</v>
+        <v>39923</v>
       </c>
       <c r="H54" s="2">
         <v>25</v>
@@ -3382,11 +3386,11 @@
       <c r="O54" s="2">
         <v>0</v>
       </c>
-      <c r="P54" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="2">
         <v>54</v>
       </c>
@@ -3398,7 +3402,7 @@
       </c>
       <c r="G55" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>29582</v>
+        <v>39680</v>
       </c>
       <c r="H55" s="2">
         <v>18</v>
@@ -3421,11 +3425,11 @@
       <c r="O55" s="2">
         <v>0</v>
       </c>
-      <c r="P55" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
         <v>55</v>
       </c>
@@ -3440,7 +3444,7 @@
       </c>
       <c r="G56" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>28541</v>
+        <v>38834</v>
       </c>
       <c r="H56" s="2">
         <v>18</v>
@@ -3463,11 +3467,11 @@
       <c r="O56" s="2">
         <v>0</v>
       </c>
-      <c r="P56" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="2">
         <v>56</v>
       </c>
@@ -3479,7 +3483,7 @@
       </c>
       <c r="G57" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>28256</v>
+        <v>38732</v>
       </c>
       <c r="H57" s="2">
         <v>26</v>
@@ -3505,11 +3509,11 @@
       <c r="O57" s="2">
         <v>0</v>
       </c>
-      <c r="P57" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2">
         <v>57</v>
       </c>
@@ -3524,7 +3528,7 @@
       </c>
       <c r="G58" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>29021</v>
+        <v>38600</v>
       </c>
       <c r="H58" s="2">
         <v>10</v>
@@ -3539,7 +3543,7 @@
         <v>1</v>
       </c>
       <c r="M58" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N58" s="2" t="s">
         <v>95</v>
@@ -3547,11 +3551,11 @@
       <c r="O58" s="2">
         <v>0</v>
       </c>
-      <c r="P58" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="2">
         <v>58</v>
       </c>
@@ -3566,7 +3570,7 @@
       </c>
       <c r="G59" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>27983</v>
+        <v>37784</v>
       </c>
       <c r="H59" s="2">
         <v>6</v>
@@ -3590,11 +3594,11 @@
       <c r="O59" s="2">
         <v>0</v>
       </c>
-      <c r="P59" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2">
         <v>59</v>
       </c>
@@ -3612,7 +3616,7 @@
       </c>
       <c r="G60" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>28100</v>
+        <v>37685</v>
       </c>
       <c r="H60" s="2">
         <v>27</v>
@@ -3636,11 +3640,11 @@
       <c r="O60" s="2">
         <v>0</v>
       </c>
-      <c r="P60" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="2">
         <v>60</v>
       </c>
@@ -3658,7 +3662,7 @@
       </c>
       <c r="G61" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>27944</v>
+        <v>38057</v>
       </c>
       <c r="H61" s="2">
         <v>27</v>
@@ -3682,951 +3686,962 @@
       <c r="O61" s="2">
         <v>0</v>
       </c>
-      <c r="P61" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="63" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="64" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+      <c r="P61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="63" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="64" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <autoFilter ref="A1:O61" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:O61" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <filterColumn colId="8">
+      <filters>
+        <filter val="Student"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="12">
+      <filters>
+        <filter val="1"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <hyperlinks>
     <hyperlink ref="F31" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="F32" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
